--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.1152791274519</v>
+        <v>4.568732858210933</v>
       </c>
       <c r="D2" t="n">
-        <v>26.95837054032121</v>
+        <v>4.380735212802196</v>
       </c>
       <c r="E2" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F2" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.99364113815123</v>
+        <v>6.986466684949574</v>
       </c>
       <c r="D3" t="n">
-        <v>42.72843755142248</v>
+        <v>6.943371102106154</v>
       </c>
       <c r="E3" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F3" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.19795562423894</v>
+        <v>7.182167788938829</v>
       </c>
       <c r="D4" t="n">
-        <v>30.09060392289334</v>
+        <v>4.889723137470169</v>
       </c>
       <c r="E4" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F4" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.0937164303999</v>
+        <v>6.190228919939984</v>
       </c>
       <c r="D5" t="n">
-        <v>27.51804621612091</v>
+        <v>4.471682510119647</v>
       </c>
       <c r="E5" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F5" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.156863916219264</v>
+        <v>1.162990386385631</v>
       </c>
       <c r="D6" t="n">
-        <v>6.994193837199116</v>
+        <v>1.136556498544856</v>
       </c>
       <c r="E6" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F6" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.39725501197996</v>
+        <v>2.177053939446744</v>
       </c>
       <c r="D7" t="n">
-        <v>13.13292629626017</v>
+        <v>2.134100523142277</v>
       </c>
       <c r="E7" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F7" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.31150252865889</v>
+        <v>2.00061916090707</v>
       </c>
       <c r="D8" t="n">
-        <v>12.23206760027829</v>
+        <v>1.987710985045222</v>
       </c>
       <c r="E8" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F8" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.29413713180193</v>
+        <v>6.060297283917813</v>
       </c>
       <c r="D9" t="n">
-        <v>37.22181454171435</v>
+        <v>6.048544863028583</v>
       </c>
       <c r="E9" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F9" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.62423728162906</v>
+        <v>7.251438558264723</v>
       </c>
       <c r="D10" t="n">
-        <v>44.17763533036157</v>
+        <v>7.178865741183756</v>
       </c>
       <c r="E10" t="n">
-        <v>14.20690983634623</v>
+        <v>2.308622848406262</v>
       </c>
       <c r="F10" t="n">
-        <v>12.76697757266784</v>
+        <v>2.074633855558524</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
